--- a/tavi_system/TAVR变量(中英对照)-25.05.30.xlsx
+++ b/tavi_system/TAVR变量(中英对照)-25.05.30.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="12870" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="278">
   <si>
     <t>基线资料</t>
   </si>
@@ -297,26 +297,7 @@
     <t>THV_Brand_name</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>字符串(ACURATE Neo, Avalus, CoreValve, Edwards, Edwards SAPIEN, Evolut, Hancock, INSPIRIS, Inoue, Inovare, J-Valve, JenaValve, LOTUS, Medtronic Mosaic, MyVal, Navitor, PERCEVAL-S, Portico, St Jude, Tyshak, Venus, Vitaflow Liberty,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Taurus Elite)</t>
-    </r>
+    <t>字符串(ACURATE Neo, Avalus, CoreValve, Edwards, Edwards SAPIEN, Evolut, Hancock, INSPIRIS, Inoue, Inovare, J-Valve, JenaValve, LOTUS, Medtronic Mosaic, MyVal, Navitor, PERCEVAL-S, Portico, St Jude, Tyshak, Venus, Vitaflow Liberty,Taurus Elite)</t>
   </si>
   <si>
     <t>心肌梗死/急性心肌梗死</t>
@@ -681,6 +662,225 @@
   </si>
   <si>
     <t>二尖瓣返流变化</t>
+  </si>
+  <si>
+    <t>Mitral_Regurgitation_Change</t>
+  </si>
+  <si>
+    <t>字符串（增加（Increase）、减少（Decrease）、无变化（Null））</t>
+  </si>
+  <si>
+    <t>瓣周漏程度</t>
+  </si>
+  <si>
+    <t>PVL_Severity_At_Last_Follow_up</t>
+  </si>
+  <si>
+    <t>抗凝药</t>
+  </si>
+  <si>
+    <t>Anticoagulant</t>
+  </si>
+  <si>
+    <t>Aortic_Valve_Flow_Velocity</t>
+  </si>
+  <si>
+    <t>尺寸过大≥15%</t>
+  </si>
+  <si>
+    <t>Oversizing_Rate_gte_15_percent</t>
+  </si>
+  <si>
+    <t>患者是否因 ​​TAVI（经导管主动脉瓣植入术）相关并发症​​ 而接受了 ​​后续干预​​（如二次手术、补救治疗等）</t>
+  </si>
+  <si>
+    <t>Subsequent_Intervention_For_TAVI_R_Complication_Occurred</t>
+  </si>
+  <si>
+    <t>他汀类药物</t>
+  </si>
+  <si>
+    <t>Statins</t>
+  </si>
+  <si>
+    <t>窦管交界高度</t>
+  </si>
+  <si>
+    <t>Sinotubular_Junction_STJ_Diameter_Height</t>
+  </si>
+  <si>
+    <t>术后是否即刻瓣周漏</t>
+  </si>
+  <si>
+    <t>TAVI_R_Immediate_PostProcedural_PVL_Occurred</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ​​后续干预的具体类型​​ 和 ​​发生时间​​（仅在发生干预时填写）</t>
+  </si>
+  <si>
+    <t>Subsequent_Intervention_Type_And_Timing_If_Occurred</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>心梗</t>
+  </si>
+  <si>
+    <t>Myocardial_Infarction_History</t>
+  </si>
+  <si>
+    <t>窦管交界直径</t>
+  </si>
+  <si>
+    <t>Sinotubular_Junction_STJ_Diameter</t>
+  </si>
+  <si>
+    <t>术后即刻瓣周漏程度</t>
+  </si>
+  <si>
+    <t>TAVI_R_Immediate_PostProcedural_PVL_Severity</t>
+  </si>
+  <si>
+    <t>字符串（微量（trace）, 轻度（mild）, 中度（moderate）, 重度（severe），N/A）‘Trivial’，‘Minimal’与‘Trace’同义</t>
+  </si>
+  <si>
+    <t>术后封堵</t>
+  </si>
+  <si>
+    <t>Occlusion_Procedure_Post_TAVI_R</t>
+  </si>
+  <si>
+    <t>布尔值</t>
+  </si>
+  <si>
+    <t>经皮冠状动脉介入术</t>
+  </si>
+  <si>
+    <t>Percutaneous_Coronary_Intervention_PCI_History</t>
+  </si>
+  <si>
+    <t>窦部直径（主动脉根部）</t>
+  </si>
+  <si>
+    <t>Sinus_Of_Valsalva_Mean_Diameter</t>
+  </si>
+  <si>
+    <t>瓣架移位</t>
+  </si>
+  <si>
+    <t>THV_Displacement_Or_Embolization</t>
+  </si>
+  <si>
+    <t>二次手术</t>
+  </si>
+  <si>
+    <t>Reoperation_Post_TAVI_R</t>
+  </si>
+  <si>
+    <t>冠状动脉旁路移植术</t>
+  </si>
+  <si>
+    <t>Coronary_Artery_Bypass_Grafting_CABG_History</t>
+  </si>
+  <si>
+    <t>升主动脉直径</t>
+  </si>
+  <si>
+    <t>Ascending_Aorta_Diameter_At_Pulmonary_Artery_Bifurcation</t>
+  </si>
+  <si>
+    <t>浮点数（e.g. 2.4 mm³）</t>
+  </si>
+  <si>
+    <t>转外科开胸手术</t>
+  </si>
+  <si>
+    <t>Conversion_To_SAVR_Required</t>
+  </si>
+  <si>
+    <t>术后中转开胸</t>
+  </si>
+  <si>
+    <t>Conversion_to_Open_Surgery_Post_TAVI_R</t>
+  </si>
+  <si>
+    <t>胸外科医师学会评分</t>
+  </si>
+  <si>
+    <t>Society_of_Thoracic_Surgeons_STS_Score</t>
+  </si>
+  <si>
+    <t>瓣环上钙化（主动脉瓣）</t>
+  </si>
+  <si>
+    <t>Aortic_Valve_Supraannular_Calcification_Volume</t>
+  </si>
+  <si>
+    <t>转心肺转流术</t>
+  </si>
+  <si>
+    <t>Cardiopulmonary_Bypass_CPB_Required</t>
+  </si>
+  <si>
+    <t>术后起搏器植入</t>
+  </si>
+  <si>
+    <t>Pacemaker_Implantation_Post_TAVI_R</t>
+  </si>
+  <si>
+    <t>氨基末端B型利钠肽前体</t>
+  </si>
+  <si>
+    <t>NT_proBNP_Level_Value</t>
+  </si>
+  <si>
+    <t>瓣环钙化（主动脉瓣）</t>
+  </si>
+  <si>
+    <t>Aortic_Valve_Annular_Calcification_Volume</t>
+  </si>
+  <si>
+    <t>瓣中瓣</t>
+  </si>
+  <si>
+    <t>Valve_In_Valve_For_Acute_Failure_Or_Malposition</t>
+  </si>
+  <si>
+    <t>术后瓣膜脱落</t>
+  </si>
+  <si>
+    <t>Valve_Dislodgement_Post_TAVI_R</t>
+  </si>
+  <si>
+    <t>钠-葡萄糖共转运蛋白2抑制剂</t>
+  </si>
+  <si>
+    <t>Sodium-Glucose Cotransporter 2 inhibitors</t>
+  </si>
+  <si>
+    <t>左心室流出道直径</t>
+  </si>
+  <si>
+    <t>Left_Ventricular_Outflow_Tract_LVOT_Diameter</t>
+  </si>
+  <si>
+    <t>围术期死亡</t>
+  </si>
+  <si>
+    <t>TAVI_R_Periprocedural_Death_In_Hospital</t>
+  </si>
+  <si>
+    <t>术后主动脉夹层</t>
+  </si>
+  <si>
+    <t>Aortic_Dissection_Post_TAVI_R</t>
+  </si>
+  <si>
+    <t>左心室流出道钙化体积</t>
+  </si>
+  <si>
+    <t>Left_Ventricular_Outflow_Tract_LVOT_Calcification_Volume</t>
   </si>
   <si>
     <r>
@@ -755,219 +955,6 @@
       </rPr>
       <t>）</t>
     </r>
-  </si>
-  <si>
-    <t>瓣周漏程度</t>
-  </si>
-  <si>
-    <t>PVL_Severity_At_Last_Follow_up</t>
-  </si>
-  <si>
-    <t>抗凝药</t>
-  </si>
-  <si>
-    <t>Anticoagulant</t>
-  </si>
-  <si>
-    <t>Aortic_Valve_Flow_Velocity</t>
-  </si>
-  <si>
-    <t>尺寸过大≥15%</t>
-  </si>
-  <si>
-    <t>Oversizing_Rate_gte_15_percent</t>
-  </si>
-  <si>
-    <t>患者是否因 ​​TAVI（经导管主动脉瓣植入术）相关并发症​​ 而接受了 ​​后续干预​​（如二次手术、补救治疗等）</t>
-  </si>
-  <si>
-    <t>Subsequent_Intervention_For_TAVI_R_Complication_Occurred</t>
-  </si>
-  <si>
-    <t>他汀类药物</t>
-  </si>
-  <si>
-    <t>Statins</t>
-  </si>
-  <si>
-    <t>窦管交界高度</t>
-  </si>
-  <si>
-    <t>Sinotubular_Junction_STJ_Diameter_Height</t>
-  </si>
-  <si>
-    <t>术后是否即刻瓣周漏</t>
-  </si>
-  <si>
-    <t>TAVI_R_Immediate_PostProcedural_PVL_Occurred</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ​​后续干预的具体类型​​ 和 ​​发生时间​​（仅在发生干预时填写）</t>
-  </si>
-  <si>
-    <t>Subsequent_Intervention_Type_And_Timing_If_Occurred</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>心梗</t>
-  </si>
-  <si>
-    <t>Myocardial_Infarction_History</t>
-  </si>
-  <si>
-    <t>窦管交界直径</t>
-  </si>
-  <si>
-    <t>Sinotubular_Junction_STJ_Diameter</t>
-  </si>
-  <si>
-    <t>术后即刻瓣周漏程度</t>
-  </si>
-  <si>
-    <t>TAVI_R_Immediate_PostProcedural_PVL_Severity</t>
-  </si>
-  <si>
-    <t>字符串（微量（trace）, 轻度（mild）, 中度（moderate）, 重度（severe），N/A）‘Trivial’，‘Minimal’与‘Trace’同义</t>
-  </si>
-  <si>
-    <t>术后封堵</t>
-  </si>
-  <si>
-    <t>Occlusion_Procedure_Post_TAVI_R</t>
-  </si>
-  <si>
-    <t>布尔值</t>
-  </si>
-  <si>
-    <t>经皮冠状动脉介入术</t>
-  </si>
-  <si>
-    <t>Percutaneous_Coronary_Intervention_PCI_History</t>
-  </si>
-  <si>
-    <t>窦部直径（主动脉根部）</t>
-  </si>
-  <si>
-    <t>Sinus_Of_Valsalva_Mean_Diameter</t>
-  </si>
-  <si>
-    <t>瓣架移位</t>
-  </si>
-  <si>
-    <t>THV_Displacement_Or_Embolization</t>
-  </si>
-  <si>
-    <t>二次手术</t>
-  </si>
-  <si>
-    <t>Reoperation_Post_TAVI_R</t>
-  </si>
-  <si>
-    <t>冠状动脉旁路移植术</t>
-  </si>
-  <si>
-    <t>Coronary_Artery_Bypass_Grafting_CABG_History</t>
-  </si>
-  <si>
-    <t>升主动脉直径</t>
-  </si>
-  <si>
-    <t>Ascending_Aorta_Diameter_At_Pulmonary_Artery_Bifurcation</t>
-  </si>
-  <si>
-    <t>浮点数（e.g. 2.4 mm³）</t>
-  </si>
-  <si>
-    <t>转外科开胸手术</t>
-  </si>
-  <si>
-    <t>Conversion_To_SAVR_Required</t>
-  </si>
-  <si>
-    <t>术后中转开胸</t>
-  </si>
-  <si>
-    <t>Conversion_to_Open_Surgery_Post_TAVI_R</t>
-  </si>
-  <si>
-    <t>胸外科医师学会评分</t>
-  </si>
-  <si>
-    <t>Society_of_Thoracic_Surgeons_STS_Score</t>
-  </si>
-  <si>
-    <t>瓣环上钙化（主动脉瓣）</t>
-  </si>
-  <si>
-    <t>Aortic_Valve_Supraannular_Calcification_Volume</t>
-  </si>
-  <si>
-    <t>转心肺转流术</t>
-  </si>
-  <si>
-    <t>Cardiopulmonary_Bypass_CPB_Required</t>
-  </si>
-  <si>
-    <t>术后起搏器植入</t>
-  </si>
-  <si>
-    <t>Pacemaker_Implantation_Post_TAVI_R</t>
-  </si>
-  <si>
-    <t>氨基末端B型利钠肽前体</t>
-  </si>
-  <si>
-    <t>NT_proBNP_Level_Value</t>
-  </si>
-  <si>
-    <t>瓣环钙化（主动脉瓣）</t>
-  </si>
-  <si>
-    <t>Aortic_Valve_Annular_Calcification_Volume</t>
-  </si>
-  <si>
-    <t>瓣中瓣</t>
-  </si>
-  <si>
-    <t>Valve_In_Valve_For_Acute_Failure_Or_Malposition</t>
-  </si>
-  <si>
-    <t>术后瓣膜脱落</t>
-  </si>
-  <si>
-    <t>Valve_Dislodgement_Post_TAVI_R</t>
-  </si>
-  <si>
-    <t>钠-葡萄糖共转运蛋白2抑制剂</t>
-  </si>
-  <si>
-    <t>Sodium-Glucose Cotransporter 2 inhibitors</t>
-  </si>
-  <si>
-    <t>左心室流出道直径</t>
-  </si>
-  <si>
-    <t>Left_Ventricular_Outflow_Tract_LVOT_Diameter</t>
-  </si>
-  <si>
-    <t>围术期死亡</t>
-  </si>
-  <si>
-    <t>TAVI_R_Periprocedural_Death_In_Hospital</t>
-  </si>
-  <si>
-    <t>术后主动脉夹层</t>
-  </si>
-  <si>
-    <t>Aortic_Dissection_Post_TAVI_R</t>
-  </si>
-  <si>
-    <t>左心室流出道钙化体积</t>
-  </si>
-  <si>
-    <t>Left_Ventricular_Outflow_Tract_LVOT_Calcification_Volume</t>
   </si>
   <si>
     <t>术后血肿</t>
@@ -1890,6 +1877,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -3441,18 +3435,18 @@
         <v>192</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>194</v>
+        <v>267</v>
       </c>
       <c r="L27" s="29"/>
       <c r="P27" s="16"/>
       <c r="Q27" s="38" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="R27" s="22" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S27" s="21" t="s">
         <v>222</v>
@@ -3461,10 +3455,10 @@
     <row r="28" ht="26.4" customHeight="1" spans="4:19">
       <c r="D28" s="16"/>
       <c r="E28" s="17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G28" s="18" t="s">
         <v>131</v>
@@ -3472,10 +3466,10 @@
       <c r="H28" s="16"/>
       <c r="P28" s="16"/>
       <c r="Q28" s="21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="R28" s="22" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="S28" s="21" t="s">
         <v>222</v>
@@ -3484,10 +3478,10 @@
     <row r="29" ht="27.75" customHeight="1" spans="4:19">
       <c r="D29" s="16"/>
       <c r="E29" s="17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G29" s="18" t="s">
         <v>131</v>
@@ -3498,19 +3492,19 @@
         <v>192</v>
       </c>
       <c r="R29" s="22" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="S29" s="22" t="s">
-        <v>194</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" ht="27.75" customHeight="1" spans="4:16">
       <c r="D30" s="16"/>
       <c r="E30" s="23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G30" s="22" t="s">
         <v>131</v>
